--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -60,7 +60,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -70,6 +70,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -449,16 +455,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32.83203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
     <col width="16.6640625" customWidth="1" style="1" min="2" max="2"/>
     <col width="14.33203125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="106.33203125" customWidth="1" style="1" min="4" max="4"/>
-    <col width="17.6640625" customWidth="1" style="1" min="5" max="5"/>
-    <col width="12.1640625" customWidth="1" style="1" min="6" max="6"/>
-    <col width="34.1640625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.1640625" customWidth="1" style="1" min="4" max="4"/>
+    <col width="106.33203125" customWidth="1" style="1" min="5" max="5"/>
+    <col width="20.83203125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="17.6640625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="12.1640625" customWidth="1" style="1" min="8" max="8"/>
+    <col width="34.1640625" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,20 +487,30 @@
       </c>
       <c r="D1" s="0" t="inlineStr">
         <is>
+          <t>nf expiration data</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
           <t>vpn pw</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>vpn expiration data</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>vpn sub emails</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>nf slots pin</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>nf sub emails</t>
         </is>
@@ -510,60 +528,77 @@
           <t>PassWord~5ef3</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="5" t="n">
+        <v>45658.98274305555</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=5bb0fc65050454d156a885e3e5a8cf7d
 https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=5bb0fc65050454d156a885e3e5a8cf7d&amp;flag=clash
 https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=5bb0fc65050454d156a885e3e5a8cf7d</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="n">
+        <v>45696.98274305555</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>liyang.tjtj@gmail.com</t>
         </is>
       </c>
-      <c r="F2" s="0" t="n"/>
-      <c r="G2" s="0" t="n"/>
+      <c r="H2" s="0" t="n"/>
+      <c r="I2" s="0" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="n"/>
       <c r="B3" s="0" t="n"/>
       <c r="C3" s="0" t="n"/>
       <c r="D3" s="0" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="0" t="n"/>
+      <c r="F3" s="0" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>772117987@qq.com</t>
         </is>
       </c>
-      <c r="F3" s="0" t="n"/>
-      <c r="G3" s="0" t="n"/>
+      <c r="H3" s="0" t="n"/>
+      <c r="I3" s="0" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n"/>
       <c r="B4" s="0" t="n"/>
       <c r="C4" s="0" t="n"/>
       <c r="D4" s="0" t="n"/>
-      <c r="E4" s="2" t="n"/>
+      <c r="E4" s="0" t="n"/>
       <c r="F4" s="0" t="n"/>
-      <c r="G4" s="0" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>993313387@qq.com</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="n"/>
+      <c r="I4" s="0" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n"/>
       <c r="B5" s="0" t="n"/>
       <c r="C5" s="0" t="n"/>
       <c r="D5" s="0" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="0" t="n"/>
-      <c r="G5" s="0" t="n"/>
+      <c r="E5" s="0" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="0" t="n"/>
+      <c r="I5" s="0" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n"/>
       <c r="B6" s="0" t="n"/>
       <c r="C6" s="0" t="n"/>
       <c r="D6" s="0" t="n"/>
-      <c r="E6" s="2" t="n"/>
+      <c r="E6" s="0" t="n"/>
       <c r="F6" s="0" t="n"/>
-      <c r="G6" s="0" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="0" t="n"/>
+      <c r="I6" s="0" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -577,92 +612,94 @@
           <t>PassWord~1915</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="D7" s="5" t="n">
+        <v>45689.98274305555</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>PassWord~42e0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="n">
+        <v>45658.98274305555</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>11@bb.com</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>2885 位置1</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>12@bb.com</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>12@bb.com</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>4517 位置2</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>liyang.tjtj@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>13@bb.com</t>
         </is>
       </c>
-      <c r="F9" s="0" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>4536 位置3</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>772117987@qq.com</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14@bb.com</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>2917 位置4</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>15@bb.com</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15@bb.com</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>4600 位置5</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>16@bb.com</t>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>993313387@qq.com</t>
         </is>
       </c>
     </row>
@@ -678,90 +715,96 @@
           <t>PassWord~9817</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="D12" s="5" t="n">
+        <v>45658.98274305555</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>PassWord~42e0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="5" t="n">
+        <v>45658.98274305555</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>17@bb.com</t>
         </is>
       </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>5746 位置1</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18@bb.com</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>18@bb.com</t>
         </is>
       </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>8374 位置2</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>19@bb.com</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>19@bb.com</t>
         </is>
       </c>
-      <c r="F14" s="0" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>8694 位置3</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>20@bb.com</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>20@bb.com</t>
         </is>
       </c>
-      <c r="F15" s="0" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>5765 位置4</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>21@bb.com</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>21@bb.com</t>
         </is>
       </c>
-      <c r="F16" s="0" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>9078 位置5</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>22@bb.com</t>
         </is>
@@ -778,32 +821,40 @@
           <t>PassWord~5b12</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
+      <c r="D17" s="5" t="n">
+        <v>45658.98274305555</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>PassWord~a3ad</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="n">
+        <v>45658.98274305555</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>22@bb.com</t>
         </is>
       </c>
+      <c r="H17" s="0" t="n"/>
+      <c r="I17" s="0" t="n"/>
     </row>
     <row r="18">
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>23@bb.com</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="E19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="E20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="E21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -816,30 +867,36 @@
           <t>PassWord~da10</t>
         </is>
       </c>
-      <c r="D22" s="0" t="inlineStr">
+      <c r="D22" s="5" t="n">
+        <v>45658.98274305555</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>PassWord~fc96</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="0" t="inlineStr">
+      <c r="F22" s="5" t="n">
+        <v>45658.98274305555</v>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>3327 位置1</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>23@bb.com</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="F23" s="0" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>1669 位置2</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>24@bb.com</t>
         </is>
@@ -858,26 +915,22 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" display="11@bb.com" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" display="11@bb.com" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" display="11@bb.com" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" display="11@bb.com" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" display="11@bb.com" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" display="11@bb.com" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" display="11@bb.com" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" display="11@bb.com" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" display="11@bb.com" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" display="11@bb.com" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" display="11@bb.com" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" display="11@bb.com" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" display="11@bb.com" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" display="11@bb.com" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" display="11@bb.com" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" display="11@bb.com" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" display="11@bb.com" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" display="11@bb.com" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" display="11@bb.com" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" display="11@bb.com" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" display="11@bb.com" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" display="11@bb.com" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -60,19 +60,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -455,14 +449,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32.83203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
     <col width="16.6640625" customWidth="1" style="1" min="2" max="2"/>
     <col width="14.33203125" customWidth="1" style="1" min="3" max="3"/>
     <col width="29.1640625" customWidth="1" style="1" min="4" max="4"/>
-    <col width="106.33203125" customWidth="1" style="1" min="5" max="5"/>
+    <col width="124" customWidth="1" style="1" min="5" max="5"/>
     <col width="20.83203125" customWidth="1" style="1" min="6" max="6"/>
     <col width="17.6640625" customWidth="1" style="1" min="7" max="7"/>
     <col width="12.1640625" customWidth="1" style="1" min="8" max="8"/>
@@ -519,394 +513,225 @@
     <row r="2" ht="64" customHeight="1" s="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>993313387@qq.com</t>
+          <t>ceshizhanghao31900@outlook.com</t>
         </is>
       </c>
       <c r="B2" s="0" t="n"/>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>PassWord~5ef3</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>45658.98274305555</v>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=5bb0fc65050454d156a885e3e5a8cf7d
-https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=5bb0fc65050454d156a885e3e5a8cf7d&amp;flag=clash
-https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=5bb0fc65050454d156a885e3e5a8cf7d</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>45696.98274305555</v>
+          <t>PassWord~1915</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>45689.98274305555</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=b4507d29d72fe0968176706c7fdbcd20</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>45695.98274305555</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>liyang.tjtj@gmail.com</t>
         </is>
       </c>
-      <c r="H2" s="0" t="n"/>
-      <c r="I2" s="0" t="n"/>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>2885 位置1</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>liyang.tjtj@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="n"/>
-      <c r="B3" s="0" t="n"/>
-      <c r="C3" s="0" t="n"/>
-      <c r="D3" s="0" t="n"/>
-      <c r="E3" s="0" t="n"/>
-      <c r="F3" s="0" t="n"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>772117987@qq.com</t>
-        </is>
-      </c>
-      <c r="H3" s="0" t="n"/>
-      <c r="I3" s="0" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>4517 位置2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="n"/>
-      <c r="B4" s="0" t="n"/>
-      <c r="C4" s="0" t="n"/>
-      <c r="D4" s="0" t="n"/>
-      <c r="E4" s="0" t="n"/>
-      <c r="F4" s="0" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>993313387@qq.com</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="n"/>
-      <c r="I4" s="0" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>4536 位置3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="n"/>
-      <c r="B5" s="0" t="n"/>
-      <c r="C5" s="0" t="n"/>
-      <c r="D5" s="0" t="n"/>
-      <c r="E5" s="0" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="0" t="n"/>
-      <c r="I5" s="0" t="n"/>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>2917 位置4</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="n"/>
-      <c r="B6" s="0" t="n"/>
-      <c r="C6" s="0" t="n"/>
-      <c r="D6" s="0" t="n"/>
-      <c r="E6" s="0" t="n"/>
-      <c r="F6" s="0" t="n"/>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="0" t="n"/>
-      <c r="I6" s="0" t="n"/>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>4600 位置5</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ceshizhanghao31900@outlook.com</t>
+          <t>ceshizhanghao31901@outlook.com</t>
         </is>
       </c>
       <c r="B7" s="0" t="n"/>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>PassWord~1915</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>45689.98274305555</v>
+          <t>PassWord~9817</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>45658.98274305555</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
           <t>PassWord~42e0</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="3" t="n">
         <v>45658.98274305555</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11@bb.com</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>2885 位置1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12@bb.com</t>
-        </is>
-      </c>
+          <t>5746 位置1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12@bb.com</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="n"/>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>4517 位置2</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>liyang.tjtj@gmail.com</t>
-        </is>
-      </c>
+          <t>8374 位置2</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>13@bb.com</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>4536 位置3</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>772117987@qq.com</t>
-        </is>
-      </c>
+          <t>8694 位置3</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14@bb.com</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>2917 位置4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15@bb.com</t>
-        </is>
-      </c>
+          <t>5765 位置4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>4600 位置5</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>993313387@qq.com</t>
-        </is>
-      </c>
+          <t>9078 位置5</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ceshizhanghao31901@outlook.com</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="n"/>
+          <t>ceshizhanghao31902@outlook.com</t>
+        </is>
+      </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>PassWord~9817</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
+          <t>PassWord~5b12</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>45658.98274305555</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>PassWord~42e0</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
+          <t>PassWord~a3ad</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>45658.98274305555</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17@bb.com</t>
-        </is>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>5746 位置1</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18@bb.com</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="0" t="n"/>
+      <c r="I12" s="0" t="n"/>
     </row>
     <row r="13">
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18@bb.com</t>
-        </is>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>8374 位置2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19@bb.com</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19@bb.com</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>8694 位置3</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20@bb.com</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>20@bb.com</t>
-        </is>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>5765 位置4</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>21@bb.com</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21@bb.com</t>
-        </is>
-      </c>
-      <c r="H16" s="0" t="inlineStr">
-        <is>
-          <t>9078 位置5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22@bb.com</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ceshizhanghao31902@outlook.com</t>
+          <t>ceshizhanghao31903@outlook.com</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>PassWord~5b12</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
+          <t>PassWord~da10</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
         <v>45658.98274305555</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>PassWord~a3ad</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
+          <t>PassWord~fc96</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>45658.98274305555</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22@bb.com</t>
-        </is>
-      </c>
-      <c r="H17" s="0" t="n"/>
-      <c r="I17" s="0" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>3327 位置1</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>23@bb.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="G19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="G20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="2" t="n"/>
-    </row>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>1669 位置2</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>ceshizhanghao31903@outlook.com</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>PassWord~da10</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>45658.98274305555</v>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>PassWord~fc96</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>45658.98274305555</v>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t>3327 位置1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>23@bb.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="H23" s="0" t="inlineStr">
-        <is>
-          <t>1669 位置2</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>24@bb.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="0" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>#endofdata</t>
         </is>
@@ -915,22 +740,10 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" display="11@bb.com" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" display="11@bb.com" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" display="11@bb.com" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" display="11@bb.com" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" display="11@bb.com" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" display="11@bb.com" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" display="11@bb.com" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" display="11@bb.com" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" display="11@bb.com" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" display="11@bb.com" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yyqq/Documents/liyang/scripts/start_2/start2/configuration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2E9C69-F6AC-974D-B0CA-A0F84BA0B183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE70A54-3B31-C149-8B10-CA18B3C0B02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>email</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>#endofdata</t>
+  </si>
+  <si>
+    <t>4517 位置5</t>
   </si>
 </sst>
 </file>
@@ -589,7 +592,7 @@
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>16</v>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -533,7 +533,11 @@
       <c r="F2" s="3" t="n">
         <v>45695.98274305555</v>
       </c>
-      <c r="G2" s="0" t="n"/>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>2106726570@qq.com</t>
+        </is>
+      </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
           <t>2885 位置1</t>
@@ -550,6 +554,11 @@
       <c r="H3" s="0" t="inlineStr">
         <is>
           <t>4517 位置2</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>2106726570@qq.com</t>
         </is>
       </c>
     </row>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -550,7 +550,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>434333050@qq.com</t>
+        </is>
+      </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
           <t>4517 位置2</t>
@@ -569,7 +573,11 @@
           <t>4536 位置3</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>434333050@qq.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="G5" s="2" t="n"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -567,7 +567,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>touchdu@163.com</t>
+        </is>
+      </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
           <t>4536 位置3</t>
@@ -580,28 +584,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>liyang.tjtj@gmail.com</t>
+        </is>
+      </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
           <t>2917 位置4</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>liyang.tjtj@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>liyang.tjtj@gmail.com</t>
-        </is>
-      </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
           <t>4600 位置5</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>liyang.tjtj@gmail.com</t>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>touchdu@163.com</t>
         </is>
       </c>
     </row>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -516,7 +516,11 @@
           <t>ceshizhanghao31900@outlook.com</t>
         </is>
       </c>
-      <c r="B2" s="0" t="n"/>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>fxmanofndzdpbtbm</t>
+        </is>
+      </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
           <t>PassWord~1915</t>
@@ -596,7 +600,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>liyang.tjtj@gmail.com</t>
+          <t>dummy@dummy.com</t>
         </is>
       </c>
     </row>
@@ -615,17 +619,21 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ceshizhanghao31901@outlook.com</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="n"/>
+          <t>ceshizhanghao31901@gmail.com</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>gmunjnrjqwxbugrk</t>
+        </is>
+      </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>PassWord~9817</t>
+          <t>PassWord~c4d</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>45658.98274305555</v>
+        <v>45689.98274305555</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -638,10 +646,14 @@
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>5746 位置1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t>1311 位置1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>liyang.tjtj@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="G8" s="2" t="n"/>
@@ -769,9 +781,10 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>dummy@dummy.com</t>
+          <t>liyang.tjtj@gmail.com</t>
         </is>
       </c>
     </row>
@@ -649,11 +649,7 @@
           <t>1311 位置1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>liyang.tjtj@gmail.com</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="G8" s="2" t="n"/>
@@ -714,7 +710,11 @@
         <v>45658.98274305555</v>
       </c>
       <c r="G12" s="2" t="n"/>
-      <c r="H12" s="0" t="n"/>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>4407 位置1</t>
+        </is>
+      </c>
       <c r="I12" s="0" t="n"/>
     </row>
     <row r="13">
@@ -781,10 +781,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yyqq/Documents/liyang/scripts/start_2/start2/configuration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB001099-6D9D-0A4D-983B-2134B71FB95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDA9A0B-7175-AE4D-8CE6-2480F45FFD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>email</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>4536 位置3</t>
-  </si>
-  <si>
-    <t>liyang.tjtj@gmail.com</t>
   </si>
   <si>
     <t>2917 位置4</t>
@@ -617,19 +614,15 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="2"/>
+      <c r="H5" t="s">
         <v>20</v>
       </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -637,76 +630,76 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
       </c>
       <c r="D7" s="3">
         <v>45699.982743055552</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
         <v>45658.982743055552</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G8" s="2"/>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G9" s="2"/>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G10" s="2"/>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G11" s="2"/>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
         <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
       </c>
       <c r="D12" s="3">
         <v>45658.982743055552</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" s="3">
         <v>45658.982743055552</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I12"/>
     </row>
@@ -724,35 +717,35 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
         <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
       </c>
       <c r="D17" s="3">
         <v>45658.982743055552</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3">
         <v>45658.982743055552</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -588,7 +588,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>zzj7810715@iCloud.com</t>
+        </is>
+      </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
           <t>2917 位置4</t>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -649,7 +649,11 @@
           <t>1311 位置1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>liyang.tjtj@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="G8" s="2" t="n"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -649,11 +649,7 @@
           <t>1311 位置1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>liyang.tjtj@gmail.com</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="G8" s="2" t="n"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -649,7 +649,11 @@
           <t>1311 位置1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>y67877687866231y@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="G8" s="2" t="n"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -605,6 +605,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>y67877687866231y@gmail.com</t>
+        </is>
+      </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
           <t>4600 位置5</t>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -667,7 +667,11 @@
           <t>8374 位置2</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>479697929@qq.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="G9" s="2" t="n"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -607,7 +607,7 @@
     <row r="6">
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>y67877687866231y@gmail.com</t>
+          <t>479697929@qq.com</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -654,11 +654,7 @@
           <t>1311 位置1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>y67877687866231y@gmail.com</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="G8" s="2" t="n"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -675,7 +675,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>leo@alu.scu.edu.cn</t>
+        </is>
+      </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
           <t>8374 位置2</t>
@@ -694,7 +698,11 @@
           <t>8694 位置3</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>leo@alu.scu.edu.cn</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="G10" s="4" t="n"/>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <family val="2"/>
       <color theme="1"/>
@@ -26,19 +26,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <family val="2"/>
       <color theme="10"/>
       <sz val="11"/>
       <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -67,7 +60,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -78,13 +71,10 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -460,17 +450,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="32.875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="16.625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="14.375" customWidth="1" style="1" min="3" max="3"/>
-    <col width="29.125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="32.83203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="16.6640625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="14.33203125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="29.1640625" customWidth="1" style="1" min="4" max="4"/>
     <col width="124" customWidth="1" style="1" min="5" max="5"/>
-    <col width="20.875" customWidth="1" style="1" min="6" max="6"/>
-    <col width="17.625" customWidth="1" style="1" min="7" max="7"/>
-    <col width="12.125" customWidth="1" style="1" min="8" max="8"/>
-    <col width="34.125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="20.83203125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="17.6640625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="12.1640625" customWidth="1" style="1" min="8" max="8"/>
+    <col width="34.1640625" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,8 +510,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="63.95" customHeight="1" s="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="64" customHeight="1" s="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ceshizhanghao31900@outlook.com</t>
         </is>
@@ -539,7 +529,7 @@
       <c r="D2" s="3" t="n">
         <v>45689.98274305555</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=b4507d29d72fe0968176706c7fdbcd20</t>
         </is>
@@ -564,7 +554,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>434333050@qq.com</t>
         </is>
@@ -581,7 +571,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>touchdu@163.com</t>
         </is>
@@ -591,14 +581,14 @@
           <t>4536 位置3</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>434333050@qq.com</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>zzj7810715@iCloud.com</t>
         </is>
@@ -608,7 +598,7 @@
           <t>2917 位置4</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>zzj7810715@iCloud.com</t>
         </is>
@@ -632,7 +622,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ceshizhanghao31901@gmail.com</t>
         </is>
@@ -650,7 +640,7 @@
       <c r="D7" s="3" t="n">
         <v>45699.98274305555</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>https://maomao.match.qqaamao.com.lmxy.cc/api/v1/client/subscribe?token=01798f929ef1692adf2a7e6f756c3b90</t>
         </is>
@@ -658,7 +648,7 @@
       <c r="F7" s="3" t="n">
         <v>45704.98274305555</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>26223@qq.com</t>
         </is>
@@ -668,73 +658,78 @@
           <t>1311 位置1</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>26223@qq.com</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>leo@alu.scu.edu.cn</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>8374 位置2</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
+          <t>6245 位置2</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>479697929@qq.com</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>8694 位置3</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+          <t>6213 位置3</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>leo@alu.scu.edu.cn</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="G10" s="4" t="n"/>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>5765 位置4</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n"/>
+          <t>1292 位置4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>9078 位置5</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n"/>
+          <t>6149 位置5</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>ceshizhanghao31902@outlook.com</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ceshizhanghao31902@gmail.com</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>fixjmyacevifgmyy</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>PassWord~5b12</t>
+          <t>PassWord~4842</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>45658.98274305555</v>
+        <v>45704.98274305555</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -744,28 +739,48 @@
       <c r="F12" s="3" t="n">
         <v>45658.98274305555</v>
       </c>
-      <c r="G12" s="4" t="n"/>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>4407 位置1</t>
+          <t>1234 位置1</t>
         </is>
       </c>
       <c r="I12" s="0" t="n"/>
     </row>
     <row r="13">
-      <c r="G13" s="4" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6169 位置2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="G14" s="4" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6188 位置3</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="G15" s="4" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1266 位置4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="G16" s="4" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6226 位置5</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>ceshizhanghao31903@outlook.com</t>
         </is>
@@ -786,13 +801,13 @@
       <c r="F17" s="3" t="n">
         <v>45658.98274305555</v>
       </c>
-      <c r="G17" s="4" t="n"/>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="0" t="inlineStr">
         <is>
           <t>3327 位置1</t>
         </is>
       </c>
-      <c r="I17" s="4" t="n"/>
+      <c r="I17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
@@ -800,11 +815,29 @@
           <t>1669 位置2</t>
         </is>
       </c>
-      <c r="I18" s="4" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+      <c r="I18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1650 位置3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3295 位置4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1714 位置5</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>

--- a/configuration/name_list.xlsx
+++ b/configuration/name_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="26640" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -701,7 +701,11 @@
           <t>1292 位置4</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ln52601314@qq.com</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="G11" s="2" t="n"/>
@@ -749,7 +753,7 @@
     </row>
     <row r="13">
       <c r="G13" s="2" t="n"/>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>6169 位置2</t>
         </is>
@@ -757,7 +761,7 @@
     </row>
     <row r="14">
       <c r="G14" s="2" t="n"/>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>6188 位置3</t>
         </is>
@@ -765,7 +769,7 @@
     </row>
     <row r="15">
       <c r="G15" s="2" t="n"/>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>1266 位置4</t>
         </is>
@@ -773,7 +777,7 @@
     </row>
     <row r="16">
       <c r="G16" s="2" t="n"/>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>6226 位置5</t>
         </is>
@@ -818,21 +822,21 @@
       <c r="I18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>1650 位置3</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>3295 位置4</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>1714 位置5</t>
         </is>
